--- a/CE国試data/CE_questions_2017.xlsx
+++ b/CE国試data/CE_questions_2017.xlsx
@@ -2075,7 +2075,7 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
@@ -4242,7 +4242,7 @@
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
@@ -8919,7 +8919,7 @@
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T86" t="inlineStr">
@@ -9409,7 +9409,7 @@
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T91" t="inlineStr">
@@ -11591,7 +11591,7 @@
       </c>
       <c r="S113" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T113" t="inlineStr">
@@ -11687,7 +11687,7 @@
       </c>
       <c r="S114" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T114" t="inlineStr">
@@ -15067,7 +15067,7 @@
       </c>
       <c r="S148" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T148" t="inlineStr">
@@ -15265,7 +15265,7 @@
       </c>
       <c r="S150" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T150" t="inlineStr">
@@ -18119,7 +18119,7 @@
       </c>
       <c r="S179" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T179" t="inlineStr">
